--- a/public/templates/pr_service_template.xlsx
+++ b/public/templates/pr_service_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OCD CARAGA\Desktop\caraga-supply\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59D7DCC-68FE-4F60-B4A2-AA4D4779AA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94A0109-A8CE-4610-BEE3-1E2478C8F96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -197,9 +197,6 @@
     <t>{{input_date}}</t>
   </si>
   <si>
-    <t>Chargeability:</t>
-  </si>
-  <si>
     <t>{{overall_cost}}</t>
   </si>
   <si>
@@ -225,6 +222,21 @@
   </si>
   <si>
     <t>{{estimated_cost}}</t>
+  </si>
+  <si>
+    <r>
+      <t>Chargeability:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> {{chargeability}}</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -234,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +384,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -891,7 +910,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1931,7 +1950,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
       <c r="I5" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="83"/>
       <c r="K5" s="83"/>
@@ -2027,23 +2046,23 @@
       <c r="F10" s="118"/>
       <c r="G10" s="119"/>
       <c r="H10" s="81" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="61" t="s">
+      <c r="J10" s="82" t="s">
         <v>47</v>
-      </c>
-      <c r="J10" s="82" t="s">
-        <v>48</v>
       </c>
       <c r="K10" s="80"/>
       <c r="L10" s="67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="41"/>
       <c r="C11" s="120" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="121"/>
       <c r="E11" s="121"/>
@@ -2058,7 +2077,7 @@
     <row r="12" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="41"/>
       <c r="C12" s="120" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="121"/>
       <c r="E12" s="121"/>
@@ -2099,7 +2118,7 @@
     <row r="15" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="41"/>
       <c r="C15" s="128" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="129"/>
       <c r="E15" s="129"/>
@@ -2293,7 +2312,7 @@
     <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B29" s="41"/>
       <c r="C29" s="125" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D29" s="126"/>
       <c r="E29" s="126"/>
@@ -2329,7 +2348,7 @@
         <v>5</v>
       </c>
       <c r="L31" s="79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
